--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124325642</v>
+        <v>124325145</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -823,19 +823,19 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjäder spillning, Mpd</t>
+          <t>Tjäder spillning , Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596534</v>
+        <v>596530</v>
       </c>
       <c r="R3" t="n">
-        <v>6924178</v>
+        <v>6924235</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124325832</v>
+        <v>124327233</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>78811</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,46 +916,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>230405</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>tjäder spillning , Mpd</t>
+          <t>Garnlav gran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596506</v>
+        <v>596459</v>
       </c>
       <c r="R4" t="n">
-        <v>6924177</v>
+        <v>6924231</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124325145</v>
+        <v>124325700</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,43 +1028,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjäder spillning , Mpd</t>
+          <t>Spår hackspett , Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596530</v>
+        <v>596521</v>
       </c>
       <c r="R5" t="n">
-        <v>6924235</v>
+        <v>6924171</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124327546</v>
+        <v>124327860</v>
       </c>
       <c r="B6" t="n">
-        <v>98021</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,34 +1152,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223597</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Jungfru Marie nycklar äldre exemplar , Mpd</t>
+          <t>Tjäder spillning .., Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596478</v>
+        <v>596528</v>
       </c>
       <c r="R6" t="n">
-        <v>6924256</v>
+        <v>6924268</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,11 +1227,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre exemplar( kommer nytt )</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124325700</v>
+        <v>124325832</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,46 +1265,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spår hackspett , Mpd</t>
+          <t>tjäder spillning , Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596521</v>
+        <v>596506</v>
       </c>
       <c r="R7" t="n">
-        <v>6924171</v>
+        <v>6924177</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,7 +1333,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1343,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1495,10 +1490,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124327860</v>
+        <v>124327546</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>98021</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1511,39 +1506,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>223597</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tjäder spillning .., Mpd</t>
+          <t>Jungfru Marie nycklar äldre exemplar , Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596528</v>
+        <v>596478</v>
       </c>
       <c r="R9" t="n">
-        <v>6924268</v>
+        <v>6924256</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1586,6 +1576,11 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre exemplar( kommer nytt )</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1612,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124327233</v>
+        <v>124325642</v>
       </c>
       <c r="B10" t="n">
-        <v>78811</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1624,41 +1619,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>230405</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Garnlav gran, Mpd</t>
+          <t>Tjäder spillning, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596459</v>
+        <v>596534</v>
       </c>
       <c r="R10" t="n">
-        <v>6924231</v>
+        <v>6924178</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124325145</v>
+        <v>124325508</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -821,21 +821,24 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>äldre spillning</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjäder spillning , Mpd</t>
+          <t>Tjäder spillnin, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596530</v>
+        <v>596536</v>
       </c>
       <c r="R3" t="n">
-        <v>6924235</v>
+        <v>6924189</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124327233</v>
+        <v>124327860</v>
       </c>
       <c r="B4" t="n">
-        <v>78811</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,41 +919,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>230405</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Garnlav gran, Mpd</t>
+          <t>Tjäder spillning .., Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596459</v>
+        <v>596528</v>
       </c>
       <c r="R4" t="n">
-        <v>6924231</v>
+        <v>6924268</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124325700</v>
+        <v>124325145</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,46 +1036,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spår hackspett , Mpd</t>
+          <t>Tjäder spillning , Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596521</v>
+        <v>596530</v>
       </c>
       <c r="R5" t="n">
-        <v>6924171</v>
+        <v>6924235</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,7 +1141,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124327860</v>
+        <v>124325642</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1172,19 +1177,19 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tjäder spillning .., Mpd</t>
+          <t>Tjäder spillning, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596528</v>
+        <v>596534</v>
       </c>
       <c r="R6" t="n">
-        <v>6924268</v>
+        <v>6924178</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124325832</v>
+        <v>124327233</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>78811</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,46 +1270,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>230405</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>tjäder spillning , Mpd</t>
+          <t>Garnlav gran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596506</v>
+        <v>596459</v>
       </c>
       <c r="R7" t="n">
-        <v>6924177</v>
+        <v>6924231</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124325508</v>
+        <v>124327546</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>98021</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,42 +1386,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>223597</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tjäder spillnin, Mpd</t>
+          <t>Jungfru Marie nycklar äldre exemplar , Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596536</v>
+        <v>596478</v>
       </c>
       <c r="R8" t="n">
-        <v>6924189</v>
+        <v>6924256</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1463,7 +1455,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre exemplar( kommer nytt )</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124327546</v>
+        <v>124325832</v>
       </c>
       <c r="B9" t="n">
-        <v>98021</v>
+        <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,34 +1503,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223597</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Jungfru Marie nycklar äldre exemplar , Mpd</t>
+          <t>tjäder spillning , Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596478</v>
+        <v>596506</v>
       </c>
       <c r="R9" t="n">
-        <v>6924256</v>
+        <v>6924177</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1565,7 +1567,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1575,12 +1577,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre exemplar( kommer nytt )</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124325642</v>
+        <v>124325700</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,43 +1616,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tjäder spillning, Mpd</t>
+          <t>Spår hackspett , Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596534</v>
+        <v>596521</v>
       </c>
       <c r="R10" t="n">
-        <v>6924178</v>
+        <v>6924171</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124325508</v>
+        <v>124325145</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -821,24 +821,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>äldre spillning</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjäder spillnin, Mpd</t>
+          <t>Tjäder spillning , Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596536</v>
+        <v>596530</v>
       </c>
       <c r="R3" t="n">
-        <v>6924189</v>
+        <v>6924235</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124327860</v>
+        <v>124327546</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>98021</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>223597</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjäder spillning .., Mpd</t>
+          <t>Jungfru Marie nycklar äldre exemplar , Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596528</v>
+        <v>596478</v>
       </c>
       <c r="R4" t="n">
-        <v>6924268</v>
+        <v>6924256</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,6 +990,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre exemplar( kommer nytt )</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124325145</v>
+        <v>124325642</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1060,19 +1057,19 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjäder spillning , Mpd</t>
+          <t>Tjäder spillning, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596530</v>
+        <v>596534</v>
       </c>
       <c r="R5" t="n">
-        <v>6924235</v>
+        <v>6924178</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124325642</v>
+        <v>124327233</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>78811</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,46 +1150,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>230405</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tjäder spillning, Mpd</t>
+          <t>Garnlav gran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596534</v>
+        <v>596459</v>
       </c>
       <c r="R6" t="n">
-        <v>6924178</v>
+        <v>6924231</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124327233</v>
+        <v>124327860</v>
       </c>
       <c r="B7" t="n">
-        <v>78811</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,41 +1262,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>230405</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Garnlav gran, Mpd</t>
+          <t>Tjäder spillning .., Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596459</v>
+        <v>596528</v>
       </c>
       <c r="R7" t="n">
-        <v>6924231</v>
+        <v>6924268</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124327546</v>
+        <v>124325508</v>
       </c>
       <c r="B8" t="n">
-        <v>98021</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,34 +1383,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223597</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jungfru Marie nycklar äldre exemplar , Mpd</t>
+          <t>Tjäder spillnin, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596478</v>
+        <v>596536</v>
       </c>
       <c r="R8" t="n">
-        <v>6924256</v>
+        <v>6924189</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,12 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre exemplar( kommer nytt )</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124325832</v>
+        <v>124325700</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,43 +1499,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>tjäder spillning , Mpd</t>
+          <t>Spår hackspett , Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596506</v>
+        <v>596521</v>
       </c>
       <c r="R9" t="n">
-        <v>6924177</v>
+        <v>6924171</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,7 +1570,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1577,7 +1580,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124325700</v>
+        <v>124325832</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,46 +1619,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Spår hackspett , Mpd</t>
+          <t>tjäder spillning , Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596521</v>
+        <v>596506</v>
       </c>
       <c r="R10" t="n">
-        <v>6924171</v>
+        <v>6924177</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124325145</v>
+        <v>124327860</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -828,14 +828,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjäder spillning , Mpd</t>
+          <t>Tjäder spillning .., Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596530</v>
+        <v>596528</v>
       </c>
       <c r="R3" t="n">
-        <v>6924235</v>
+        <v>6924268</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124327546</v>
+        <v>124325642</v>
       </c>
       <c r="B4" t="n">
-        <v>98021</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223597</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Jungfru Marie nycklar äldre exemplar , Mpd</t>
+          <t>Tjäder spillning, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596478</v>
+        <v>596534</v>
       </c>
       <c r="R4" t="n">
-        <v>6924256</v>
+        <v>6924178</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre exemplar( kommer nytt )</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124325642</v>
+        <v>124327546</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>98021</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,39 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>223597</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjäder spillning, Mpd</t>
+          <t>Jungfru Marie nycklar äldre exemplar , Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596534</v>
+        <v>596478</v>
       </c>
       <c r="R5" t="n">
-        <v>6924178</v>
+        <v>6924256</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre exemplar( kommer nytt )</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124327233</v>
+        <v>124325832</v>
       </c>
       <c r="B6" t="n">
-        <v>78811</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,41 +1150,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>230405</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Garnlav gran, Mpd</t>
+          <t>tjäder spillning , Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596459</v>
+        <v>596506</v>
       </c>
       <c r="R6" t="n">
-        <v>6924231</v>
+        <v>6924177</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124327860</v>
+        <v>124325700</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,43 +1267,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tjäder spillning .., Mpd</t>
+          <t>Spår hackspett , Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596528</v>
+        <v>596521</v>
       </c>
       <c r="R7" t="n">
-        <v>6924268</v>
+        <v>6924171</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1348,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,7 +1375,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124325508</v>
+        <v>124325145</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
@@ -1401,24 +1409,21 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>äldre spillning</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tjäder spillnin, Mpd</t>
+          <t>Tjäder spillning , Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596536</v>
+        <v>596530</v>
       </c>
       <c r="R8" t="n">
-        <v>6924189</v>
+        <v>6924235</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,7 +1455,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1465,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1492,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124325700</v>
+        <v>124327233</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>78811</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,45 +1508,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>230405</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Spår hackspett , Mpd</t>
+          <t>Garnlav gran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596521</v>
+        <v>596459</v>
       </c>
       <c r="R9" t="n">
-        <v>6924171</v>
+        <v>6924231</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1570,7 +1567,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1580,7 +1577,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,7 +1604,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124325832</v>
+        <v>124325508</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1641,21 +1638,24 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>äldre spillning</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>tjäder spillning , Mpd</t>
+          <t>Tjäder spillnin, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596506</v>
+        <v>596536</v>
       </c>
       <c r="R10" t="n">
-        <v>6924177</v>
+        <v>6924189</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124327860</v>
+        <v>124325391</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -828,14 +828,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjäder spillning .., Mpd</t>
+          <t>Tjäder spillning , Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596528</v>
+        <v>596530</v>
       </c>
       <c r="R3" t="n">
-        <v>6924268</v>
+        <v>6924235</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124325642</v>
+        <v>124327860</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -940,19 +940,19 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjäder spillning, Mpd</t>
+          <t>Tjäder spillning .., Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596534</v>
+        <v>596528</v>
       </c>
       <c r="R4" t="n">
-        <v>6924178</v>
+        <v>6924268</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124327546</v>
+        <v>124325700</v>
       </c>
       <c r="B5" t="n">
-        <v>98021</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,38 +1033,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223597</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jungfru Marie nycklar äldre exemplar , Mpd</t>
+          <t>Spår hackspett , Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596478</v>
+        <v>596521</v>
       </c>
       <c r="R5" t="n">
-        <v>6924256</v>
+        <v>6924171</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre exemplar( kommer nytt )</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1255,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124325700</v>
+        <v>124327546</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>98021</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,46 +1270,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>223597</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spår hackspett , Mpd</t>
+          <t>Jungfru Marie nycklar äldre exemplar , Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596521</v>
+        <v>596478</v>
       </c>
       <c r="R7" t="n">
-        <v>6924171</v>
+        <v>6924256</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,7 +1333,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1343,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre exemplar( kommer nytt )</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124325145</v>
+        <v>124327233</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>78811</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,46 +1387,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>230405</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tjäder spillning , Mpd</t>
+          <t>Garnlav gran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596530</v>
+        <v>596459</v>
       </c>
       <c r="R8" t="n">
-        <v>6924235</v>
+        <v>6924231</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1455,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124327233</v>
+        <v>124325642</v>
       </c>
       <c r="B9" t="n">
-        <v>78811</v>
+        <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,41 +1499,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>230405</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Garnlav gran, Mpd</t>
+          <t>Tjäder spillning, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596459</v>
+        <v>596534</v>
       </c>
       <c r="R9" t="n">
-        <v>6924231</v>
+        <v>6924178</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1258,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124327546</v>
+        <v>124327233</v>
       </c>
       <c r="B7" t="n">
-        <v>98021</v>
+        <v>78811</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,41 +1270,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223597</v>
+        <v>230405</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jungfru Marie nycklar äldre exemplar , Mpd</t>
+          <t>Garnlav gran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596478</v>
+        <v>596459</v>
       </c>
       <c r="R7" t="n">
-        <v>6924256</v>
+        <v>6924231</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,12 +1343,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre exemplar( kommer nytt )</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124327233</v>
+        <v>124325642</v>
       </c>
       <c r="B8" t="n">
-        <v>78811</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,41 +1382,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>230405</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Garnlav gran, Mpd</t>
+          <t>Tjäder spillning, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596459</v>
+        <v>596534</v>
       </c>
       <c r="R8" t="n">
-        <v>6924231</v>
+        <v>6924178</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,7 +1487,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124325642</v>
+        <v>124325508</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
@@ -1521,21 +1521,24 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tjäder spillning, Mpd</t>
+          <t>Tjäder spillnin, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596534</v>
+        <v>596536</v>
       </c>
       <c r="R9" t="n">
-        <v>6924178</v>
+        <v>6924189</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,7 +1570,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1577,7 +1580,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124325508</v>
+        <v>124932344</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,46 +1619,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tjäder spillnin, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596536</v>
+        <v>596451</v>
       </c>
       <c r="R10" t="n">
-        <v>6924189</v>
+        <v>6924184</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1682,22 +1682,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,15 +1717,965 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124933195</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98124</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>596511</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6924206</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>Linnea Silverliv</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>Linnea Silverliv</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124933097</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>596542</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6924248</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>124932515</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>596444</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6924201</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>124932906</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>596516</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6924223</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>124933132</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>596530</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6924227</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>124933330</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>596540</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6924247</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>124932553</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98122</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>596460</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6924249</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>124933179</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>596533</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6924242</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -1607,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124932344</v>
+        <v>124933195</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>98124</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,43 +1619,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596451</v>
+        <v>596511</v>
       </c>
       <c r="R10" t="n">
-        <v>6924184</v>
+        <v>6924206</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1697,12 +1696,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,22 +1711,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124933195</v>
+        <v>124932344</v>
       </c>
       <c r="B11" t="n">
-        <v>98124</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,42 +1735,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596511</v>
+        <v>596451</v>
       </c>
       <c r="R11" t="n">
-        <v>6924206</v>
+        <v>6924184</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1808,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1818,7 +1813,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,12 +1833,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124325391</v>
+        <v>124327233</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>78811</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,46 +799,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>230405</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjäder spillning , Mpd</t>
+          <t>Garnlav gran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596530</v>
+        <v>596459</v>
       </c>
       <c r="R3" t="n">
-        <v>6924235</v>
+        <v>6924231</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124327860</v>
+        <v>124325832</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -945,14 +940,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjäder spillning .., Mpd</t>
+          <t>tjäder spillning , Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596528</v>
+        <v>596506</v>
       </c>
       <c r="R4" t="n">
-        <v>6924268</v>
+        <v>6924177</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124325700</v>
+        <v>124325145</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,46 +1028,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spår hackspett , Mpd</t>
+          <t>Tjäder spillning , Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596521</v>
+        <v>596530</v>
       </c>
       <c r="R5" t="n">
-        <v>6924171</v>
+        <v>6924235</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,7 +1133,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124325832</v>
+        <v>124325642</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1177,19 +1169,19 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>tjäder spillning , Mpd</t>
+          <t>Tjäder spillning, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596506</v>
+        <v>596534</v>
       </c>
       <c r="R6" t="n">
-        <v>6924177</v>
+        <v>6924178</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124327233</v>
+        <v>124325700</v>
       </c>
       <c r="B7" t="n">
-        <v>78811</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,37 +1266,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>230405</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Garnlav gran, Mpd</t>
+          <t>Spår hackspett , Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596459</v>
+        <v>596521</v>
       </c>
       <c r="R7" t="n">
-        <v>6924231</v>
+        <v>6924171</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,7 +1370,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124325642</v>
+        <v>124327860</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
@@ -1406,19 +1406,19 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tjäder spillning, Mpd</t>
+          <t>Tjäder spillning .., Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596534</v>
+        <v>596528</v>
       </c>
       <c r="R8" t="n">
-        <v>6924178</v>
+        <v>6924268</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1607,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124933195</v>
+        <v>124933097</v>
       </c>
       <c r="B10" t="n">
-        <v>98124</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,42 +1619,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596511</v>
+        <v>596542</v>
       </c>
       <c r="R10" t="n">
-        <v>6924206</v>
+        <v>6924248</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1687,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,7 +1697,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,12 +1717,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1845,10 +1851,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124933097</v>
+        <v>124932553</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>98122</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1857,43 +1863,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596542</v>
+        <v>596460</v>
       </c>
       <c r="R12" t="n">
-        <v>6924248</v>
+        <v>6924249</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1925,7 +1926,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1935,12 +1936,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,22 +1951,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124932515</v>
+        <v>124933179</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,16 +1979,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2008,14 +2004,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596444</v>
+        <v>596533</v>
       </c>
       <c r="R13" t="n">
-        <v>6924201</v>
+        <v>6924242</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2047,7 +2043,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2057,7 +2053,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2072,12 +2073,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2206,10 +2207,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124933132</v>
+        <v>124933330</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2218,43 +2219,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596530</v>
+        <v>596540</v>
       </c>
       <c r="R15" t="n">
-        <v>6924227</v>
+        <v>6924247</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2286,7 +2287,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2296,12 +2297,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2316,22 +2312,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124933330</v>
+        <v>124933132</v>
       </c>
       <c r="B16" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2340,43 +2336,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596540</v>
+        <v>596530</v>
       </c>
       <c r="R16" t="n">
-        <v>6924247</v>
+        <v>6924227</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2408,7 +2404,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2418,7 +2414,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2433,22 +2434,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124932553</v>
+        <v>124933195</v>
       </c>
       <c r="B17" t="n">
-        <v>98122</v>
+        <v>98124</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2461,34 +2462,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596460</v>
+        <v>596511</v>
       </c>
       <c r="R17" t="n">
-        <v>6924249</v>
+        <v>6924206</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2520,7 +2525,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2530,7 +2535,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2545,22 +2550,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124933179</v>
+        <v>124932515</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2573,16 +2578,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2598,14 +2603,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596533</v>
+        <v>596444</v>
       </c>
       <c r="R18" t="n">
-        <v>6924242</v>
+        <v>6924201</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2637,7 +2642,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2647,12 +2652,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2667,12 +2667,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124327233</v>
+        <v>124325832</v>
       </c>
       <c r="B3" t="n">
-        <v>78811</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,41 +799,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>230405</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Garnlav gran, Mpd</t>
+          <t>tjäder spillning , Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596459</v>
+        <v>596506</v>
       </c>
       <c r="R3" t="n">
-        <v>6924231</v>
+        <v>6924177</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124325832</v>
+        <v>124327233</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>78811</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,46 +916,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>230405</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>tjäder spillning , Mpd</t>
+          <t>Garnlav gran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596506</v>
+        <v>596459</v>
       </c>
       <c r="R4" t="n">
-        <v>6924177</v>
+        <v>6924231</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124325145</v>
+        <v>124325642</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1052,19 +1052,19 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjäder spillning , Mpd</t>
+          <t>Tjäder spillning, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596530</v>
+        <v>596534</v>
       </c>
       <c r="R5" t="n">
-        <v>6924235</v>
+        <v>6924178</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,7 +1133,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124325642</v>
+        <v>124325145</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1169,19 +1169,19 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tjäder spillning, Mpd</t>
+          <t>Tjäder spillning , Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596534</v>
+        <v>596530</v>
       </c>
       <c r="R6" t="n">
-        <v>6924178</v>
+        <v>6924235</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124325700</v>
+        <v>124325508</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,25 +1262,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1288,20 +1288,20 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spår hackspett , Mpd</t>
+          <t>Tjäder spillnin, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596521</v>
+        <v>596536</v>
       </c>
       <c r="R7" t="n">
-        <v>6924171</v>
+        <v>6924189</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124327860</v>
+        <v>124325700</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,43 +1382,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tjäder spillning .., Mpd</t>
+          <t>Spår hackspett , Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596528</v>
+        <v>596521</v>
       </c>
       <c r="R8" t="n">
-        <v>6924268</v>
+        <v>6924171</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,7 +1453,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1463,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,7 +1490,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124325508</v>
+        <v>124327860</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
@@ -1521,24 +1524,21 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>äldre spillning</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tjäder spillnin, Mpd</t>
+          <t>Tjäder spillning .., Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596536</v>
+        <v>596528</v>
       </c>
       <c r="R9" t="n">
-        <v>6924189</v>
+        <v>6924268</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124933097</v>
+        <v>124933195</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>98124</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,43 +1619,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596542</v>
+        <v>596511</v>
       </c>
       <c r="R10" t="n">
-        <v>6924248</v>
+        <v>6924206</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1697,12 +1696,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,22 +1711,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124932344</v>
+        <v>124933330</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,31 +1735,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1774,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596451</v>
+        <v>596540</v>
       </c>
       <c r="R11" t="n">
-        <v>6924184</v>
+        <v>6924247</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1809,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1819,12 +1813,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1839,22 +1828,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124932553</v>
+        <v>124932906</v>
       </c>
       <c r="B12" t="n">
-        <v>98122</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1863,38 +1852,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596460</v>
+        <v>596516</v>
       </c>
       <c r="R12" t="n">
-        <v>6924249</v>
+        <v>6924223</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1926,7 +1920,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1936,7 +1930,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,22 +1950,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124933179</v>
+        <v>124932515</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1979,16 +1978,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2004,14 +2003,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596533</v>
+        <v>596444</v>
       </c>
       <c r="R13" t="n">
-        <v>6924242</v>
+        <v>6924201</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2043,7 +2042,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2053,12 +2052,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2073,19 +2067,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124932906</v>
+        <v>124933179</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -2121,19 +2115,19 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596516</v>
+        <v>596533</v>
       </c>
       <c r="R14" t="n">
-        <v>6924223</v>
+        <v>6924242</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2165,7 +2159,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2175,12 +2169,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2195,22 +2189,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124933330</v>
+        <v>124933097</v>
       </c>
       <c r="B15" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2219,31 +2213,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2252,10 +2246,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596540</v>
+        <v>596542</v>
       </c>
       <c r="R15" t="n">
-        <v>6924247</v>
+        <v>6924248</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2287,7 +2281,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2297,7 +2291,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2324,10 +2323,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124933132</v>
+        <v>124932553</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>98122</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2336,43 +2335,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596530</v>
+        <v>596460</v>
       </c>
       <c r="R16" t="n">
-        <v>6924227</v>
+        <v>6924249</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2404,7 +2398,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2414,12 +2408,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2434,22 +2423,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124933195</v>
+        <v>124932344</v>
       </c>
       <c r="B17" t="n">
-        <v>98124</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2458,42 +2447,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596511</v>
+        <v>596451</v>
       </c>
       <c r="R17" t="n">
-        <v>6924206</v>
+        <v>6924184</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2525,7 +2515,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2535,7 +2525,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2550,22 +2545,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124932515</v>
+        <v>124933132</v>
       </c>
       <c r="B18" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2578,16 +2573,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2607,10 +2602,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596444</v>
+        <v>596530</v>
       </c>
       <c r="R18" t="n">
-        <v>6924201</v>
+        <v>6924227</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2642,7 +2637,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2652,7 +2647,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124325832</v>
+        <v>124327860</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -828,14 +828,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>tjäder spillning , Mpd</t>
+          <t>Tjäder spillning .., Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596506</v>
+        <v>596528</v>
       </c>
       <c r="R3" t="n">
-        <v>6924177</v>
+        <v>6924268</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124327233</v>
+        <v>124325832</v>
       </c>
       <c r="B4" t="n">
-        <v>78811</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,41 +916,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>230405</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Garnlav gran, Mpd</t>
+          <t>tjäder spillning , Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596459</v>
+        <v>596506</v>
       </c>
       <c r="R4" t="n">
-        <v>6924231</v>
+        <v>6924177</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124325642</v>
+        <v>124325145</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1052,19 +1057,19 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjäder spillning, Mpd</t>
+          <t>Tjäder spillning , Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596534</v>
+        <v>596530</v>
       </c>
       <c r="R5" t="n">
-        <v>6924178</v>
+        <v>6924235</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,7 +1138,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124325145</v>
+        <v>124325642</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1169,19 +1174,19 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tjäder spillning , Mpd</t>
+          <t>Tjäder spillning, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596530</v>
+        <v>596534</v>
       </c>
       <c r="R6" t="n">
-        <v>6924235</v>
+        <v>6924178</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124325508</v>
+        <v>124325700</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,25 +1267,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1288,20 +1293,20 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tjäder spillnin, Mpd</t>
+          <t>Spår hackspett , Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596536</v>
+        <v>596521</v>
       </c>
       <c r="R7" t="n">
-        <v>6924189</v>
+        <v>6924171</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,7 +1348,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124325700</v>
+        <v>124325508</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,25 +1387,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1408,20 +1413,20 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spår hackspett , Mpd</t>
+          <t>Tjäder spillnin, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596521</v>
+        <v>596536</v>
       </c>
       <c r="R8" t="n">
-        <v>6924171</v>
+        <v>6924189</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,7 +1458,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1463,7 +1468,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,10 +1495,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124327860</v>
+        <v>124327233</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>78811</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1502,46 +1507,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>230405</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tjäder spillning .., Mpd</t>
+          <t>Garnlav gran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596528</v>
+        <v>596459</v>
       </c>
       <c r="R9" t="n">
-        <v>6924268</v>
+        <v>6924231</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124933195</v>
+        <v>124933330</v>
       </c>
       <c r="B10" t="n">
-        <v>98124</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,38 +1623,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596511</v>
+        <v>596540</v>
       </c>
       <c r="R10" t="n">
-        <v>6924206</v>
+        <v>6924247</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1687,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,7 +1697,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,22 +1712,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124933330</v>
+        <v>124933132</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1735,43 +1736,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596540</v>
+        <v>596530</v>
       </c>
       <c r="R11" t="n">
-        <v>6924247</v>
+        <v>6924227</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1803,7 +1804,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,7 +1814,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,22 +1834,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124932906</v>
+        <v>124933195</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>98124</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1852,31 +1858,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1885,10 +1890,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596516</v>
+        <v>596511</v>
       </c>
       <c r="R12" t="n">
-        <v>6924223</v>
+        <v>6924206</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1920,7 +1925,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1930,12 +1935,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1950,22 +1950,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124932515</v>
+        <v>124932553</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>98122</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1974,43 +1974,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596444</v>
+        <v>596460</v>
       </c>
       <c r="R13" t="n">
-        <v>6924201</v>
+        <v>6924249</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2042,7 +2037,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2052,7 +2047,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,22 +2062,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124933179</v>
+        <v>124932515</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2095,16 +2090,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2120,14 +2115,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596533</v>
+        <v>596444</v>
       </c>
       <c r="R14" t="n">
-        <v>6924242</v>
+        <v>6924201</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2159,7 +2154,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2169,12 +2164,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2189,19 +2179,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124933097</v>
+        <v>124932906</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2237,19 +2227,19 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596542</v>
+        <v>596516</v>
       </c>
       <c r="R15" t="n">
-        <v>6924248</v>
+        <v>6924223</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2281,7 +2271,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2291,12 +2281,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2311,22 +2301,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124932553</v>
+        <v>124932344</v>
       </c>
       <c r="B16" t="n">
-        <v>98122</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2335,38 +2325,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596460</v>
+        <v>596451</v>
       </c>
       <c r="R16" t="n">
-        <v>6924249</v>
+        <v>6924184</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2398,7 +2393,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2408,7 +2403,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2435,7 +2435,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124932344</v>
+        <v>124933097</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2480,10 +2480,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596451</v>
+        <v>596542</v>
       </c>
       <c r="R17" t="n">
-        <v>6924184</v>
+        <v>6924248</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2545,19 +2545,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124933132</v>
+        <v>124933179</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2598,14 +2598,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596530</v>
+        <v>596533</v>
       </c>
       <c r="R18" t="n">
-        <v>6924227</v>
+        <v>6924242</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2647,12 +2647,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2667,12 +2667,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124327860</v>
+        <v>124325145</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -828,14 +828,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjäder spillning .., Mpd</t>
+          <t>Tjäder spillning , Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596528</v>
+        <v>596530</v>
       </c>
       <c r="R3" t="n">
-        <v>6924268</v>
+        <v>6924235</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124325832</v>
+        <v>124325508</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -938,21 +938,24 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>äldre spillning</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>tjäder spillning , Mpd</t>
+          <t>Tjäder spillnin, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596506</v>
+        <v>596536</v>
       </c>
       <c r="R4" t="n">
-        <v>6924177</v>
+        <v>6924189</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,7 +1024,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124325145</v>
+        <v>124325642</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1057,19 +1060,19 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjäder spillning , Mpd</t>
+          <t>Tjäder spillning, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596530</v>
+        <v>596534</v>
       </c>
       <c r="R5" t="n">
-        <v>6924235</v>
+        <v>6924178</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124325642</v>
+        <v>124327233</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>78811</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,46 +1153,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>230405</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tjäder spillning, Mpd</t>
+          <t>Garnlav gran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596534</v>
+        <v>596459</v>
       </c>
       <c r="R6" t="n">
-        <v>6924178</v>
+        <v>6924231</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124325700</v>
+        <v>124327860</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,46 +1265,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spår hackspett , Mpd</t>
+          <t>Tjäder spillning .., Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596521</v>
+        <v>596528</v>
       </c>
       <c r="R7" t="n">
-        <v>6924171</v>
+        <v>6924268</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,7 +1333,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1343,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,7 +1370,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124325508</v>
+        <v>124325832</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
@@ -1409,24 +1404,21 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>äldre spillning</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tjäder spillnin, Mpd</t>
+          <t>tjäder spillning , Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596536</v>
+        <v>596506</v>
       </c>
       <c r="R8" t="n">
-        <v>6924189</v>
+        <v>6924177</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1468,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124327233</v>
+        <v>124325700</v>
       </c>
       <c r="B9" t="n">
-        <v>78811</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1511,37 +1503,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>230405</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Garnlav gran, Mpd</t>
+          <t>Spår hackspett , Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596459</v>
+        <v>596521</v>
       </c>
       <c r="R9" t="n">
-        <v>6924231</v>
+        <v>6924171</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124933330</v>
+        <v>124933179</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,31 +1619,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596540</v>
+        <v>596533</v>
       </c>
       <c r="R10" t="n">
-        <v>6924247</v>
+        <v>6924242</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1697,7 +1697,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1724,7 +1729,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124933132</v>
+        <v>124932344</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1765,14 +1770,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596530</v>
+        <v>596451</v>
       </c>
       <c r="R11" t="n">
-        <v>6924227</v>
+        <v>6924184</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1804,7 +1809,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1814,12 +1819,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,22 +1839,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124933195</v>
+        <v>124932906</v>
       </c>
       <c r="B12" t="n">
-        <v>98124</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1858,30 +1863,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1890,10 +1896,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596511</v>
+        <v>596516</v>
       </c>
       <c r="R12" t="n">
-        <v>6924206</v>
+        <v>6924223</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1925,7 +1931,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1935,7 +1941,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1950,22 +1961,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124932553</v>
+        <v>124932515</v>
       </c>
       <c r="B13" t="n">
-        <v>98122</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1974,38 +1985,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596460</v>
+        <v>596444</v>
       </c>
       <c r="R13" t="n">
-        <v>6924249</v>
+        <v>6924201</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2037,7 +2053,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2047,7 +2063,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2062,22 +2078,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124932515</v>
+        <v>124933132</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2090,16 +2106,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2119,10 +2135,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596444</v>
+        <v>596530</v>
       </c>
       <c r="R14" t="n">
-        <v>6924201</v>
+        <v>6924227</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2154,7 +2170,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2164,7 +2180,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2191,10 +2212,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124932906</v>
+        <v>124933195</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>98124</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2203,31 +2224,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2236,10 +2256,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596516</v>
+        <v>596511</v>
       </c>
       <c r="R15" t="n">
-        <v>6924223</v>
+        <v>6924206</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2271,7 +2291,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2281,12 +2301,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2301,22 +2316,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124932344</v>
+        <v>124933330</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2325,31 +2340,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2358,10 +2373,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596451</v>
+        <v>596540</v>
       </c>
       <c r="R16" t="n">
-        <v>6924184</v>
+        <v>6924247</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2393,7 +2408,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2403,12 +2418,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2423,22 +2433,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124933097</v>
+        <v>124932553</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>98122</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2447,43 +2457,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596542</v>
+        <v>596460</v>
       </c>
       <c r="R17" t="n">
-        <v>6924248</v>
+        <v>6924249</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2515,7 +2520,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2525,12 +2530,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2545,19 +2545,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124933179</v>
+        <v>124933097</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2602,10 +2602,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596533</v>
+        <v>596542</v>
       </c>
       <c r="R18" t="n">
-        <v>6924242</v>
+        <v>6924248</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124325508</v>
+        <v>124325700</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,25 +916,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,20 +942,20 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjäder spillnin, Mpd</t>
+          <t>Spår hackspett , Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596536</v>
+        <v>596521</v>
       </c>
       <c r="R4" t="n">
-        <v>6924189</v>
+        <v>6924171</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,7 +1024,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124325642</v>
+        <v>124325832</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1060,19 +1060,19 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjäder spillning, Mpd</t>
+          <t>tjäder spillning , Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596534</v>
+        <v>596506</v>
       </c>
       <c r="R5" t="n">
-        <v>6924178</v>
+        <v>6924177</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124327233</v>
+        <v>124325508</v>
       </c>
       <c r="B6" t="n">
-        <v>78811</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,41 +1153,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>230405</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Garnlav gran, Mpd</t>
+          <t>Tjäder spillnin, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596459</v>
+        <v>596536</v>
       </c>
       <c r="R6" t="n">
-        <v>6924231</v>
+        <v>6924189</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1370,10 +1378,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124325832</v>
+        <v>124327233</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>78811</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,46 +1390,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>230405</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>tjäder spillning , Mpd</t>
+          <t>Garnlav gran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596506</v>
+        <v>596459</v>
       </c>
       <c r="R8" t="n">
-        <v>6924177</v>
+        <v>6924231</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1450,7 +1453,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1463,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1490,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124325700</v>
+        <v>124325642</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,46 +1502,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Spår hackspett , Mpd</t>
+          <t>Tjäder spillning, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596521</v>
+        <v>596534</v>
       </c>
       <c r="R9" t="n">
-        <v>6924171</v>
+        <v>6924178</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,7 +1607,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124933179</v>
+        <v>124933132</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1648,14 +1648,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596533</v>
+        <v>596530</v>
       </c>
       <c r="R10" t="n">
-        <v>6924242</v>
+        <v>6924227</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1697,12 +1697,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,19 +1717,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124932344</v>
+        <v>124932906</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1765,19 +1765,19 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596451</v>
+        <v>596516</v>
       </c>
       <c r="R11" t="n">
-        <v>6924184</v>
+        <v>6924223</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1819,12 +1819,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1839,19 +1839,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124932906</v>
+        <v>124933097</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1887,19 +1887,19 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596516</v>
+        <v>596542</v>
       </c>
       <c r="R12" t="n">
-        <v>6924223</v>
+        <v>6924248</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1961,22 +1961,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124932515</v>
+        <v>124932553</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>98122</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1985,43 +1985,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596444</v>
+        <v>596460</v>
       </c>
       <c r="R13" t="n">
-        <v>6924201</v>
+        <v>6924249</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2053,7 +2048,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2063,7 +2058,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2078,22 +2073,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124933132</v>
+        <v>124933330</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2102,43 +2097,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596530</v>
+        <v>596540</v>
       </c>
       <c r="R14" t="n">
-        <v>6924227</v>
+        <v>6924247</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2170,7 +2165,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2180,12 +2175,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2200,12 +2190,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2328,10 +2318,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124933330</v>
+        <v>124932344</v>
       </c>
       <c r="B16" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2340,31 +2330,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2373,10 +2363,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596540</v>
+        <v>596451</v>
       </c>
       <c r="R16" t="n">
-        <v>6924247</v>
+        <v>6924184</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2408,7 +2398,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2418,7 +2408,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2433,22 +2428,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124932553</v>
+        <v>124933179</v>
       </c>
       <c r="B17" t="n">
-        <v>98122</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2457,38 +2452,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596460</v>
+        <v>596533</v>
       </c>
       <c r="R17" t="n">
-        <v>6924249</v>
+        <v>6924242</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2530,7 +2530,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2545,22 +2550,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124933097</v>
+        <v>124932515</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2573,16 +2578,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2598,14 +2603,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596542</v>
+        <v>596444</v>
       </c>
       <c r="R18" t="n">
-        <v>6924248</v>
+        <v>6924201</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2637,7 +2642,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2647,12 +2652,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2667,12 +2667,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124325145</v>
+        <v>124325391</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124325700</v>
+        <v>124325508</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,25 +916,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,20 +942,20 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spår hackspett , Mpd</t>
+          <t>Tjäder spillnin, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596521</v>
+        <v>596536</v>
       </c>
       <c r="R4" t="n">
-        <v>6924171</v>
+        <v>6924189</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,7 +1024,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124325832</v>
+        <v>124327860</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1065,14 +1065,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>tjäder spillning , Mpd</t>
+          <t>Tjäder spillning .., Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596506</v>
+        <v>596528</v>
       </c>
       <c r="R5" t="n">
-        <v>6924177</v>
+        <v>6924268</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,7 +1141,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124325508</v>
+        <v>124325642</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1175,24 +1175,21 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tjäder spillnin, Mpd</t>
+          <t>Tjäder spillning, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596536</v>
+        <v>596534</v>
       </c>
       <c r="R6" t="n">
-        <v>6924189</v>
+        <v>6924178</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,7 +1258,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124327860</v>
+        <v>124325832</v>
       </c>
       <c r="B7" t="n">
         <v>56722</v>
@@ -1302,14 +1299,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tjäder spillning .., Mpd</t>
+          <t>tjäder spillning , Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596528</v>
+        <v>596506</v>
       </c>
       <c r="R7" t="n">
-        <v>6924268</v>
+        <v>6924177</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1351,7 +1348,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124327233</v>
+        <v>124325700</v>
       </c>
       <c r="B8" t="n">
-        <v>78811</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,37 +1391,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>230405</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Garnlav gran, Mpd</t>
+          <t>Spår hackspett , Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596459</v>
+        <v>596521</v>
       </c>
       <c r="R8" t="n">
-        <v>6924231</v>
+        <v>6924171</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1453,7 +1458,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1463,7 +1468,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,10 +1495,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124325642</v>
+        <v>124327233</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>78811</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1502,46 +1507,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>230405</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tjäder spillning, Mpd</t>
+          <t>Garnlav gran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596534</v>
+        <v>596459</v>
       </c>
       <c r="R9" t="n">
-        <v>6924178</v>
+        <v>6924231</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -1973,10 +1973,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124932553</v>
+        <v>124933330</v>
       </c>
       <c r="B13" t="n">
-        <v>98122</v>
+        <v>56722</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1989,34 +1989,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596460</v>
+        <v>596540</v>
       </c>
       <c r="R13" t="n">
-        <v>6924249</v>
+        <v>6924247</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2048,7 +2053,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2058,7 +2063,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2073,22 +2078,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124933330</v>
+        <v>124932553</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
+        <v>98122</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2101,39 +2106,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596540</v>
+        <v>596460</v>
       </c>
       <c r="R14" t="n">
-        <v>6924247</v>
+        <v>6924249</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2190,12 +2190,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124325508</v>
+        <v>124325642</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -938,24 +938,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjäder spillnin, Mpd</t>
+          <t>Tjäder spillning, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596536</v>
+        <v>596534</v>
       </c>
       <c r="R4" t="n">
-        <v>6924189</v>
+        <v>6924178</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1141,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124325642</v>
+        <v>124327233</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>78811</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,46 +1150,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>230405</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tjäder spillning, Mpd</t>
+          <t>Garnlav gran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596534</v>
+        <v>596459</v>
       </c>
       <c r="R6" t="n">
-        <v>6924178</v>
+        <v>6924231</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1495,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124327233</v>
+        <v>124325508</v>
       </c>
       <c r="B9" t="n">
-        <v>78811</v>
+        <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1507,41 +1499,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>230405</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Garnlav gran, Mpd</t>
+          <t>Tjäder spillnin, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596459</v>
+        <v>596536</v>
       </c>
       <c r="R9" t="n">
-        <v>6924231</v>
+        <v>6924189</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124933132</v>
+        <v>124933195</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>98124</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,31 +1619,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1652,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596530</v>
+        <v>596511</v>
       </c>
       <c r="R10" t="n">
-        <v>6924227</v>
+        <v>6924206</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1697,12 +1696,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,22 +1711,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124932906</v>
+        <v>124933330</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,43 +1735,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596516</v>
+        <v>596540</v>
       </c>
       <c r="R11" t="n">
-        <v>6924223</v>
+        <v>6924247</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1809,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1819,12 +1813,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1839,22 +1828,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124933097</v>
+        <v>124932515</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1867,16 +1856,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1892,14 +1881,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596542</v>
+        <v>596444</v>
       </c>
       <c r="R12" t="n">
-        <v>6924248</v>
+        <v>6924201</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1931,7 +1920,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1941,12 +1930,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1961,22 +1945,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124933330</v>
+        <v>124933179</v>
       </c>
       <c r="B13" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1985,31 +1969,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2018,10 +2002,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596540</v>
+        <v>596533</v>
       </c>
       <c r="R13" t="n">
-        <v>6924247</v>
+        <v>6924242</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2053,7 +2037,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2063,7 +2047,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2090,10 +2079,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124932553</v>
+        <v>124932906</v>
       </c>
       <c r="B14" t="n">
-        <v>98122</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2102,38 +2091,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596460</v>
+        <v>596516</v>
       </c>
       <c r="R14" t="n">
-        <v>6924249</v>
+        <v>6924223</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2165,7 +2159,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2175,7 +2169,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2190,22 +2189,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124933195</v>
+        <v>124932553</v>
       </c>
       <c r="B15" t="n">
-        <v>98124</v>
+        <v>98122</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2218,38 +2217,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596511</v>
+        <v>596460</v>
       </c>
       <c r="R15" t="n">
-        <v>6924206</v>
+        <v>6924249</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2281,7 +2276,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2291,7 +2286,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,19 +2301,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124932344</v>
+        <v>124933097</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
@@ -2363,10 +2358,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596451</v>
+        <v>596542</v>
       </c>
       <c r="R16" t="n">
-        <v>6924184</v>
+        <v>6924248</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2398,7 +2393,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2408,7 +2403,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2428,19 +2423,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124933179</v>
+        <v>124932344</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2485,10 +2480,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596533</v>
+        <v>596451</v>
       </c>
       <c r="R17" t="n">
-        <v>6924242</v>
+        <v>6924184</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2520,7 +2515,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2530,7 +2525,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2550,22 +2545,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124932515</v>
+        <v>124933132</v>
       </c>
       <c r="B18" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2578,16 +2573,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2607,10 +2602,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596444</v>
+        <v>596530</v>
       </c>
       <c r="R18" t="n">
-        <v>6924201</v>
+        <v>6924227</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2642,7 +2637,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2652,7 +2647,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -1607,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124933195</v>
+        <v>124932515</v>
       </c>
       <c r="B10" t="n">
-        <v>98124</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,30 +1619,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1651,10 +1652,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596511</v>
+        <v>596444</v>
       </c>
       <c r="R10" t="n">
-        <v>6924206</v>
+        <v>6924201</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1687,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,7 +1697,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,12 +1712,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1840,10 +1841,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124932515</v>
+        <v>124933132</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1856,16 +1857,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1885,10 +1886,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596444</v>
+        <v>596530</v>
       </c>
       <c r="R12" t="n">
-        <v>6924201</v>
+        <v>6924227</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1920,7 +1921,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1930,7 +1931,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,7 +1963,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124933179</v>
+        <v>124933097</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -2002,10 +2008,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596533</v>
+        <v>596542</v>
       </c>
       <c r="R13" t="n">
-        <v>6924242</v>
+        <v>6924248</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2037,7 +2043,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2047,7 +2053,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2079,10 +2085,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124932906</v>
+        <v>124933195</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>98124</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2091,31 +2097,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2124,10 +2129,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596516</v>
+        <v>596511</v>
       </c>
       <c r="R14" t="n">
-        <v>6924223</v>
+        <v>6924206</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2159,7 +2164,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2169,12 +2174,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2189,12 +2189,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2313,7 +2313,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124933097</v>
+        <v>124933179</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596542</v>
+        <v>596533</v>
       </c>
       <c r="R16" t="n">
-        <v>6924248</v>
+        <v>6924242</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2557,7 +2557,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124933132</v>
+        <v>124932906</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2593,7 +2593,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2602,10 +2602,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596530</v>
+        <v>596516</v>
       </c>
       <c r="R18" t="n">
-        <v>6924227</v>
+        <v>6924223</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -1607,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124932515</v>
+        <v>124933097</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,16 +1623,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1648,14 +1648,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596444</v>
+        <v>596542</v>
       </c>
       <c r="R10" t="n">
-        <v>6924201</v>
+        <v>6924248</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1697,7 +1697,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,22 +1717,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124933330</v>
+        <v>124933195</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
+        <v>98124</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,39 +1745,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>219847</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596540</v>
+        <v>596511</v>
       </c>
       <c r="R11" t="n">
-        <v>6924247</v>
+        <v>6924206</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1804,7 +1808,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1814,7 +1818,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1829,22 +1833,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124933132</v>
+        <v>124932515</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1857,16 +1861,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1886,10 +1890,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596530</v>
+        <v>596444</v>
       </c>
       <c r="R12" t="n">
-        <v>6924227</v>
+        <v>6924201</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1921,7 +1925,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1931,12 +1935,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1963,7 +1962,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124933097</v>
+        <v>124933179</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -2008,10 +2007,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596542</v>
+        <v>596533</v>
       </c>
       <c r="R13" t="n">
-        <v>6924248</v>
+        <v>6924242</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2043,7 +2042,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2053,7 +2052,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2085,10 +2084,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124933195</v>
+        <v>124933330</v>
       </c>
       <c r="B14" t="n">
-        <v>98124</v>
+        <v>56722</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2101,38 +2100,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219847</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596511</v>
+        <v>596540</v>
       </c>
       <c r="R14" t="n">
-        <v>6924206</v>
+        <v>6924247</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2189,22 +2189,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124932553</v>
+        <v>124932344</v>
       </c>
       <c r="B15" t="n">
-        <v>98122</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2213,38 +2213,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596460</v>
+        <v>596451</v>
       </c>
       <c r="R15" t="n">
-        <v>6924249</v>
+        <v>6924184</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2276,7 +2281,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2286,7 +2291,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2313,7 +2323,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124933179</v>
+        <v>124932906</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
@@ -2349,19 +2359,19 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596533</v>
+        <v>596516</v>
       </c>
       <c r="R16" t="n">
-        <v>6924242</v>
+        <v>6924223</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2393,7 +2403,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2403,12 +2413,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2423,19 +2433,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124932344</v>
+        <v>124933132</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2476,14 +2486,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596451</v>
+        <v>596530</v>
       </c>
       <c r="R17" t="n">
-        <v>6924184</v>
+        <v>6924227</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2515,7 +2525,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2525,12 +2535,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2545,22 +2555,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124932906</v>
+        <v>124932553</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>98122</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2569,43 +2579,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596516</v>
+        <v>596460</v>
       </c>
       <c r="R18" t="n">
-        <v>6924223</v>
+        <v>6924249</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2637,7 +2642,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2647,12 +2652,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2667,12 +2667,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -1607,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124933097</v>
+        <v>124932515</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,16 +1623,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1648,14 +1648,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596542</v>
+        <v>596444</v>
       </c>
       <c r="R10" t="n">
-        <v>6924248</v>
+        <v>6924201</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1697,12 +1697,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,22 +1712,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124933195</v>
+        <v>124933097</v>
       </c>
       <c r="B11" t="n">
-        <v>98124</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,42 +1736,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596511</v>
+        <v>596542</v>
       </c>
       <c r="R11" t="n">
-        <v>6924206</v>
+        <v>6924248</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1808,7 +1804,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1818,7 +1814,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,22 +1834,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124932515</v>
+        <v>124933330</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1857,43 +1858,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596444</v>
+        <v>596540</v>
       </c>
       <c r="R12" t="n">
-        <v>6924201</v>
+        <v>6924247</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1925,7 +1926,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1935,7 +1936,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1950,19 +1951,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124933179</v>
+        <v>124932906</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1998,19 +1999,19 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596533</v>
+        <v>596516</v>
       </c>
       <c r="R13" t="n">
-        <v>6924242</v>
+        <v>6924223</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2042,7 +2043,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2052,12 +2053,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2072,22 +2073,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124933330</v>
+        <v>124933132</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2096,43 +2097,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596540</v>
+        <v>596530</v>
       </c>
       <c r="R14" t="n">
-        <v>6924247</v>
+        <v>6924227</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2164,7 +2165,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2174,7 +2175,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2189,19 +2195,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124932344</v>
+        <v>124933179</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2246,10 +2252,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596451</v>
+        <v>596533</v>
       </c>
       <c r="R15" t="n">
-        <v>6924184</v>
+        <v>6924242</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2281,7 +2287,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2291,7 +2297,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2311,22 +2317,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124932906</v>
+        <v>124933195</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>98124</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2335,31 +2341,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2368,10 +2373,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596516</v>
+        <v>596511</v>
       </c>
       <c r="R16" t="n">
-        <v>6924223</v>
+        <v>6924206</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2403,7 +2408,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2413,12 +2418,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2433,19 +2433,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124933132</v>
+        <v>124932344</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2486,14 +2486,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596530</v>
+        <v>596451</v>
       </c>
       <c r="R17" t="n">
-        <v>6924227</v>
+        <v>6924184</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2535,12 +2535,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2555,12 +2555,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -2445,10 +2445,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124932344</v>
+        <v>124932553</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>98122</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2457,43 +2457,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596451</v>
+        <v>596460</v>
       </c>
       <c r="R17" t="n">
-        <v>6924184</v>
+        <v>6924249</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2525,7 +2520,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2535,12 +2530,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2567,10 +2557,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124932553</v>
+        <v>124932344</v>
       </c>
       <c r="B18" t="n">
-        <v>98122</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2579,38 +2569,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596460</v>
+        <v>596451</v>
       </c>
       <c r="R18" t="n">
-        <v>6924249</v>
+        <v>6924184</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2642,7 +2637,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2652,7 +2647,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -1607,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124932515</v>
+        <v>124933330</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,43 +1619,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596444</v>
+        <v>596540</v>
       </c>
       <c r="R10" t="n">
-        <v>6924201</v>
+        <v>6924247</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,22 +1712,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124933097</v>
+        <v>124932515</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,16 +1740,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1765,14 +1765,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596542</v>
+        <v>596444</v>
       </c>
       <c r="R11" t="n">
-        <v>6924248</v>
+        <v>6924201</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1814,12 +1814,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,22 +1829,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124933330</v>
+        <v>124933195</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>98124</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1862,39 +1857,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>219847</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596540</v>
+        <v>596511</v>
       </c>
       <c r="R12" t="n">
-        <v>6924247</v>
+        <v>6924206</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1926,7 +1920,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1936,7 +1930,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,19 +1945,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124932906</v>
+        <v>124933179</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1999,19 +1993,19 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596516</v>
+        <v>596533</v>
       </c>
       <c r="R13" t="n">
-        <v>6924223</v>
+        <v>6924242</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2043,7 +2037,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2053,12 +2047,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2073,19 +2067,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124933132</v>
+        <v>124932344</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -2126,14 +2120,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596530</v>
+        <v>596451</v>
       </c>
       <c r="R14" t="n">
-        <v>6924227</v>
+        <v>6924184</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2165,7 +2159,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2175,12 +2169,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2195,22 +2189,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124933179</v>
+        <v>124932553</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>98122</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2219,43 +2213,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596533</v>
+        <v>596460</v>
       </c>
       <c r="R15" t="n">
-        <v>6924242</v>
+        <v>6924249</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2287,7 +2276,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2297,12 +2286,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2317,22 +2301,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124933195</v>
+        <v>124933097</v>
       </c>
       <c r="B16" t="n">
-        <v>98124</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2341,42 +2325,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596511</v>
+        <v>596542</v>
       </c>
       <c r="R16" t="n">
-        <v>6924206</v>
+        <v>6924248</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2408,7 +2393,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2418,7 +2403,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2433,22 +2423,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124932553</v>
+        <v>124933132</v>
       </c>
       <c r="B17" t="n">
-        <v>98122</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2457,38 +2447,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596460</v>
+        <v>596530</v>
       </c>
       <c r="R17" t="n">
-        <v>6924249</v>
+        <v>6924227</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2520,7 +2515,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2530,7 +2525,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2545,19 +2545,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124932344</v>
+        <v>124932906</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2593,19 +2593,19 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596451</v>
+        <v>596516</v>
       </c>
       <c r="R18" t="n">
-        <v>6924184</v>
+        <v>6924223</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2647,12 +2647,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2667,12 +2667,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -1607,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124933330</v>
+        <v>124932906</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,43 +1619,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596540</v>
+        <v>596516</v>
       </c>
       <c r="R10" t="n">
-        <v>6924247</v>
+        <v>6924223</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1697,7 +1697,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,22 +1717,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124932515</v>
+        <v>124933132</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>57635</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,16 +1745,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1769,10 +1774,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596444</v>
+        <v>596530</v>
       </c>
       <c r="R11" t="n">
-        <v>6924201</v>
+        <v>6924227</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1804,7 +1809,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1814,7 +1819,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1841,10 +1851,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124933195</v>
+        <v>124933330</v>
       </c>
       <c r="B12" t="n">
-        <v>98124</v>
+        <v>56836</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1857,38 +1867,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219847</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596511</v>
+        <v>596540</v>
       </c>
       <c r="R12" t="n">
-        <v>6924206</v>
+        <v>6924247</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1920,7 +1931,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1930,7 +1941,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1945,22 +1956,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124933179</v>
+        <v>124932344</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2002,10 +2013,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596533</v>
+        <v>596451</v>
       </c>
       <c r="R13" t="n">
-        <v>6924242</v>
+        <v>6924184</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2037,7 +2048,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2047,7 +2058,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2067,22 +2078,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124932344</v>
+        <v>124933179</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2124,10 +2135,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596451</v>
+        <v>596533</v>
       </c>
       <c r="R14" t="n">
-        <v>6924184</v>
+        <v>6924242</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2159,7 +2170,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2169,7 +2180,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2189,22 +2200,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124932553</v>
+        <v>124932515</v>
       </c>
       <c r="B15" t="n">
-        <v>98122</v>
+        <v>57632</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2213,38 +2224,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596460</v>
+        <v>596444</v>
       </c>
       <c r="R15" t="n">
-        <v>6924249</v>
+        <v>6924201</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2276,7 +2292,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2286,7 +2302,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2301,12 +2317,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2316,7 +2332,7 @@
         <v>124933097</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2435,10 +2451,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124933132</v>
+        <v>124933195</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>98292</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2447,31 +2463,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2480,10 +2495,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596530</v>
+        <v>596511</v>
       </c>
       <c r="R17" t="n">
-        <v>6924227</v>
+        <v>6924206</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2515,7 +2530,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2525,12 +2540,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2545,22 +2555,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124932906</v>
+        <v>124932553</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>98290</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2569,43 +2579,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596516</v>
+        <v>596460</v>
       </c>
       <c r="R18" t="n">
-        <v>6924223</v>
+        <v>6924249</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2637,7 +2642,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2647,12 +2652,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2667,12 +2667,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -1607,7 +1607,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124932906</v>
+        <v>124933097</v>
       </c>
       <c r="B10" t="n">
         <v>57635</v>
@@ -1643,19 +1643,19 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596516</v>
+        <v>596542</v>
       </c>
       <c r="R10" t="n">
-        <v>6924223</v>
+        <v>6924248</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1697,12 +1697,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,22 +1717,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124933132</v>
+        <v>124933330</v>
       </c>
       <c r="B11" t="n">
-        <v>57635</v>
+        <v>56836</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,43 +1741,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596530</v>
+        <v>596540</v>
       </c>
       <c r="R11" t="n">
-        <v>6924227</v>
+        <v>6924247</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1819,12 +1819,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1839,22 +1834,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124933330</v>
+        <v>124933132</v>
       </c>
       <c r="B12" t="n">
-        <v>56836</v>
+        <v>57635</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1863,43 +1858,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596540</v>
+        <v>596530</v>
       </c>
       <c r="R12" t="n">
-        <v>6924247</v>
+        <v>6924227</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1931,7 +1926,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1941,7 +1936,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1956,19 +1956,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124932344</v>
+        <v>124932906</v>
       </c>
       <c r="B13" t="n">
         <v>57635</v>
@@ -2004,19 +2004,19 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596451</v>
+        <v>596516</v>
       </c>
       <c r="R13" t="n">
-        <v>6924184</v>
+        <v>6924223</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2058,12 +2058,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2078,22 +2078,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124933179</v>
+        <v>124932515</v>
       </c>
       <c r="B14" t="n">
-        <v>57635</v>
+        <v>57632</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2106,16 +2106,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2131,14 +2131,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596533</v>
+        <v>596444</v>
       </c>
       <c r="R14" t="n">
-        <v>6924242</v>
+        <v>6924201</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2180,12 +2180,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2200,22 +2195,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124932515</v>
+        <v>124932344</v>
       </c>
       <c r="B15" t="n">
-        <v>57632</v>
+        <v>57635</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2228,16 +2223,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2253,14 +2248,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596444</v>
+        <v>596451</v>
       </c>
       <c r="R15" t="n">
-        <v>6924201</v>
+        <v>6924184</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2292,7 +2287,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2302,7 +2297,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2317,19 +2317,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124933097</v>
+        <v>124933179</v>
       </c>
       <c r="B16" t="n">
         <v>57635</v>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596542</v>
+        <v>596533</v>
       </c>
       <c r="R16" t="n">
-        <v>6924248</v>
+        <v>6924242</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2451,10 +2451,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124933195</v>
+        <v>124932553</v>
       </c>
       <c r="B17" t="n">
-        <v>98292</v>
+        <v>98290</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2467,38 +2467,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596511</v>
+        <v>596460</v>
       </c>
       <c r="R17" t="n">
-        <v>6924206</v>
+        <v>6924249</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2530,7 +2526,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2540,7 +2536,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2555,22 +2551,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124932553</v>
+        <v>124933195</v>
       </c>
       <c r="B18" t="n">
-        <v>98290</v>
+        <v>98292</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2583,34 +2579,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596460</v>
+        <v>596511</v>
       </c>
       <c r="R18" t="n">
-        <v>6924249</v>
+        <v>6924206</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2667,12 +2667,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -1607,43 +1607,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124933097</v>
+        <v>124933330</v>
       </c>
       <c r="B10" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56836</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1652,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596542</v>
+        <v>596540</v>
       </c>
       <c r="R10" t="n">
-        <v>6924248</v>
+        <v>6924247</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,7 +1682,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1697,12 +1692,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,43 +1719,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124933330</v>
+        <v>124933179</v>
       </c>
       <c r="B11" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1774,10 +1759,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596540</v>
+        <v>596533</v>
       </c>
       <c r="R11" t="n">
-        <v>6924247</v>
+        <v>6924242</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1809,7 +1794,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1819,7 +1804,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1846,16 +1836,11 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124933132</v>
+        <v>124932344</v>
       </c>
       <c r="B12" t="n">
         <v>57635</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1887,14 +1872,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596530</v>
+        <v>596451</v>
       </c>
       <c r="R12" t="n">
-        <v>6924227</v>
+        <v>6924184</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1926,7 +1911,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1936,12 +1921,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1956,27 +1941,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124932906</v>
+        <v>124932515</v>
       </c>
       <c r="B13" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,16 +1964,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2004,7 +1984,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2013,10 +1993,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596516</v>
+        <v>596444</v>
       </c>
       <c r="R13" t="n">
-        <v>6924223</v>
+        <v>6924201</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2048,7 +2028,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2058,12 +2038,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2090,15 +2065,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124932515</v>
+        <v>124933097</v>
       </c>
       <c r="B14" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2106,16 +2076,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2131,14 +2101,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596444</v>
+        <v>596542</v>
       </c>
       <c r="R14" t="n">
-        <v>6924201</v>
+        <v>6924248</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2170,7 +2140,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2180,7 +2150,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2195,67 +2170,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124932344</v>
+        <v>124932553</v>
       </c>
       <c r="B15" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98290</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596451</v>
+        <v>596460</v>
       </c>
       <c r="R15" t="n">
-        <v>6924184</v>
+        <v>6924249</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2287,7 +2252,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2297,12 +2262,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2329,16 +2289,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124933179</v>
+        <v>124933132</v>
       </c>
       <c r="B16" t="n">
         <v>57635</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>NT</t>
@@ -2370,14 +2325,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596533</v>
+        <v>596530</v>
       </c>
       <c r="R16" t="n">
-        <v>6924242</v>
+        <v>6924227</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2409,7 +2364,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2419,12 +2374,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2439,27 +2394,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124932553</v>
+        <v>124933195</v>
       </c>
       <c r="B17" t="n">
-        <v>98290</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98292</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2467,34 +2417,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596460</v>
+        <v>596511</v>
       </c>
       <c r="R17" t="n">
-        <v>6924249</v>
+        <v>6924206</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2526,7 +2480,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2536,7 +2490,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2551,54 +2505,50 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124933195</v>
+        <v>124932906</v>
       </c>
       <c r="B18" t="n">
-        <v>98292</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2607,10 +2557,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596511</v>
+        <v>596516</v>
       </c>
       <c r="R18" t="n">
-        <v>6924206</v>
+        <v>6924223</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2642,7 +2592,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2652,7 +2602,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2667,12 +2622,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -1370,12 +1370,7 @@
         <v>124325700</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1956,7 +1951,7 @@
         <v>124932515</v>
       </c>
       <c r="B13" t="n">
-        <v>57632</v>
+        <v>57658</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>124325700</v>
       </c>
       <c r="B8" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>124932515</v>
       </c>
       <c r="B13" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>124325700</v>
       </c>
       <c r="B8" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>124932515</v>
       </c>
       <c r="B13" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>124325700</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>124932515</v>
       </c>
       <c r="B13" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>124325700</v>
       </c>
       <c r="B8" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>124932515</v>
       </c>
       <c r="B13" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>124325700</v>
       </c>
       <c r="B8" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>124932515</v>
       </c>
       <c r="B13" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -1717,7 +1717,7 @@
         <v>124933179</v>
       </c>
       <c r="B11" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>124932344</v>
       </c>
       <c r="B12" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>124933097</v>
       </c>
       <c r="B14" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>124933132</v>
       </c>
       <c r="B16" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>124932906</v>
       </c>
       <c r="B18" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -1717,7 +1717,7 @@
         <v>124933179</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>124932344</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>124933097</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>124933132</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>124932906</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105899204</v>
+        <v>132921996</v>
       </c>
       <c r="B2" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjärdalsberget, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596469.8965691403</v>
+        <v>596403</v>
       </c>
       <c r="R2" t="n">
-        <v>6924222.636510116</v>
+        <v>6924236</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,70 +770,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Dennis Jonason</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Dennis Jonason</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124325391</v>
+        <v>132921997</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjäder spillning , Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596530</v>
+        <v>596403</v>
       </c>
       <c r="R3" t="n">
-        <v>6924235</v>
+        <v>6924236</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,70 +877,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124325642</v>
+        <v>132921998</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjäder spillning, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596534</v>
+        <v>596410</v>
       </c>
       <c r="R4" t="n">
-        <v>6924178</v>
+        <v>6924243</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,70 +984,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124327860</v>
+        <v>132921999</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6426</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjäder spillning .., Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596528</v>
+        <v>596412</v>
       </c>
       <c r="R5" t="n">
-        <v>6924268</v>
+        <v>6924247</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,22 +1061,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,27 +1091,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124327233</v>
+        <v>132922000</v>
       </c>
       <c r="B6" t="n">
-        <v>78811</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,37 +1114,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>230405</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Garnlav gran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596459</v>
+        <v>596414</v>
       </c>
       <c r="R6" t="n">
-        <v>6924231</v>
+        <v>6924271</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,22 +1168,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,27 +1198,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124325832</v>
+        <v>124325700</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,39 +1221,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>tjäder spillning , Mpd</t>
+          <t>Spår hackspett , Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596506</v>
+        <v>596521</v>
       </c>
       <c r="R7" t="n">
-        <v>6924177</v>
+        <v>6924171</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1288,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1298,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,14 +1325,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124325700</v>
+        <v>124932515</v>
       </c>
       <c r="B8" t="n">
-        <v>57681</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1396,24 +1354,21 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spår hackspett , Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596521</v>
+        <v>596444</v>
       </c>
       <c r="R8" t="n">
-        <v>6924171</v>
+        <v>6924201</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,22 +1395,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,70 +1425,62 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124325508</v>
+        <v>124932344</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tjäder spillnin, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596536</v>
+        <v>596451</v>
       </c>
       <c r="R9" t="n">
-        <v>6924189</v>
+        <v>6924184</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1560,22 +1507,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,62 +1542,62 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124933330</v>
+        <v>124932906</v>
       </c>
       <c r="B10" t="n">
-        <v>56836</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596540</v>
+        <v>596516</v>
       </c>
       <c r="R10" t="n">
-        <v>6924247</v>
+        <v>6924223</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1629,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1687,7 +1639,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,22 +1659,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124933179</v>
+        <v>124933097</v>
       </c>
       <c r="B11" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,10 +1711,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596533</v>
+        <v>596542</v>
       </c>
       <c r="R11" t="n">
-        <v>6924242</v>
+        <v>6924248</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,7 +1746,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1799,7 +1756,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1831,10 +1788,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124932344</v>
+        <v>124933132</v>
       </c>
       <c r="B12" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,14 +1824,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596451</v>
+        <v>596530</v>
       </c>
       <c r="R12" t="n">
-        <v>6924184</v>
+        <v>6924227</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1906,7 +1863,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1916,12 +1873,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,22 +1893,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124932515</v>
+        <v>124933179</v>
       </c>
       <c r="B13" t="n">
-        <v>57681</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,16 +1916,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1984,14 +1941,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596444</v>
+        <v>596533</v>
       </c>
       <c r="R13" t="n">
-        <v>6924201</v>
+        <v>6924242</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,7 +1980,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2033,7 +1990,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2048,62 +2010,62 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124933097</v>
+        <v>124325145</v>
       </c>
       <c r="B14" t="n">
-        <v>57741</v>
+        <v>57141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Tjäder spillning , Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596542</v>
+        <v>596530</v>
       </c>
       <c r="R14" t="n">
-        <v>6924248</v>
+        <v>6924235</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,27 +2092,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,22 +2122,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124932553</v>
+        <v>124325508</v>
       </c>
       <c r="B15" t="n">
-        <v>98290</v>
+        <v>57141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2188,34 +2145,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Tjäder spillnin, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596460</v>
+        <v>596536</v>
       </c>
       <c r="R15" t="n">
-        <v>6924249</v>
+        <v>6924189</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2242,22 +2207,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2272,62 +2237,62 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124933132</v>
+        <v>124325642</v>
       </c>
       <c r="B16" t="n">
-        <v>57741</v>
+        <v>57141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Tjäder spillning, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596530</v>
+        <v>596534</v>
       </c>
       <c r="R16" t="n">
-        <v>6924227</v>
+        <v>6924178</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2354,27 +2319,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2389,22 +2349,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124933195</v>
+        <v>124325832</v>
       </c>
       <c r="B17" t="n">
-        <v>98292</v>
+        <v>57141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2412,38 +2372,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219847</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>tjäder spillning , Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596511</v>
+        <v>596506</v>
       </c>
       <c r="R17" t="n">
-        <v>6924206</v>
+        <v>6924177</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2470,22 +2431,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2512,50 +2473,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124932906</v>
+        <v>124327860</v>
       </c>
       <c r="B18" t="n">
-        <v>57741</v>
+        <v>57141</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Tjäder spillning .., Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596516</v>
+        <v>596528</v>
       </c>
       <c r="R18" t="n">
-        <v>6924223</v>
+        <v>6924268</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2582,27 +2543,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2617,15 +2573,898 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>124424009</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Tjäderbajs, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>596558</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6924204</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Dropping</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
           <t>Joel Helker-Nygren</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
+      <c r="AX19" t="inlineStr">
         <is>
           <t>Joel Helker-Nygren</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>124921802</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>596419</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6924273</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>124924660</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>596399</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6924236</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>124933330</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>596540</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6924247</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132922001</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>596464</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6924305</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Fem fjädrar i fint skick från tjädertupp.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>105899204</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Tjärdalsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>596470</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6924222</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Dennis Jonason</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Dennis Jonason</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>124932553</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>596460</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6924249</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>124327233</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Garnlav gran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>596459</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6924231</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16933-2025 artfynd.xlsx
+++ b/artfynd/A 16933-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921996</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921997</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921998</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921999</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132922000</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1322,6 +1352,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124325700</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1434,6 +1469,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124932515</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1551,6 +1591,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124932344</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1668,6 +1713,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124932906</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1785,6 +1835,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124933097</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1902,6 +1957,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124933132</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2019,6 +2079,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124933179</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2131,6 +2196,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124325145</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2246,6 +2316,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124325508</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2358,6 +2433,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124325642</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2470,6 +2550,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124325832</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2582,6 +2667,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124327860</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2689,6 +2779,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124424009</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2810,6 +2905,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124921802</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2922,6 +3022,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124924660</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3034,6 +3139,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124933330</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3154,6 +3264,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132922001</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3251,6 +3366,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105899204</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3358,6 +3478,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124932553</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3465,8 +3590,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124327233</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>